--- a/result/price_comparison_2026-10-12.xlsx
+++ b/result/price_comparison_2026-10-12.xlsx
@@ -634,7 +634,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Считаются только товары, найденные у поставщиков с производителем ГАЗ/УАЗ.</t>
+          <t>Считаются только товары, найденные у поставщиков с производителем ГАЗ/УАЗ, ЗМЗ, УМЗ.</t>
         </is>
       </c>
     </row>
@@ -20175,49 +20175,48 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Росзапчасть</t>
+          <t>УАЗ Автоград</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>006900310302400</t>
+          <t>0069-00-3103024-00</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>УАЗ</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>УАЗ</t>
-        </is>
-      </c>
+          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ 2</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>оригинал</t>
+          <t>не указан</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Кольцо подшипника ступицы упорное УАЗ-452,469,3151,3163 Патриот</t>
+          <t>Кольцо упорное подшипников ступицы колеса  (min   10)**</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>ШТ</t>
-        </is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>213</v>
       </c>
       <c r="M48" s="10" t="n">
-        <v>1550</v>
+        <v>42.5</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>KZT</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1550</v>
+        <v>227.37</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -20226,14 +20225,22 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>производитель не указан или указан не бренд</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ 2»</t>
+        </is>
+      </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>Лист_1, строка 4017</t>
+          <t>По алфавиту, строка 4059</t>
         </is>
       </c>
     </row>
@@ -20258,48 +20265,49 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>УАЗ Автоград</t>
+          <t>Росзапчасть</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0069-00-3103024-00</t>
+          <t>006900310302400</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ 2</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>УАЗ</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>УАЗ</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>не указан</t>
+          <t>оригинал</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Кольцо упорное подшипников ступицы колеса  (min   10)**</t>
+          <t>Кольцо подшипника ступицы упорное УАЗ-452,469,3151,3163 Патриот</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="L49" t="n">
-        <v>213</v>
+          <t>ШТ</t>
+        </is>
       </c>
       <c r="M49" s="10" t="n">
-        <v>42.5</v>
+        <v>1550</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>KZT</t>
         </is>
       </c>
       <c r="O49" s="3" t="n">
-        <v>227.37</v>
+        <v>1550</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -20308,22 +20316,14 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>производитель не указан или указан не бренд</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ 2»</t>
-        </is>
-      </c>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 4059</t>
+          <t>Лист_1, строка 4017</t>
         </is>
       </c>
     </row>
@@ -27285,17 +27285,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>УАЗ Автоград</t>
+          <t>Росзапчасть</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>3160-00-3501076-02</t>
+          <t>316000350107602</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>ОАО УАЗ</t>
+          <t>УАЗ</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -27310,27 +27310,27 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Диск тормозной передний УАЗ  ОАО "УАЗ" **</t>
+          <t>Диск переднего тормоза 3160</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>ШТ</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>278</v>
+        <v>1</v>
       </c>
       <c r="M128" s="10" t="n">
-        <v>1950</v>
+        <v>19800</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>KZT</t>
         </is>
       </c>
       <c r="O128" s="3" t="n">
-        <v>10432.5</v>
+        <v>19800</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 2467</t>
+          <t>Лист_1, строка 2802</t>
         </is>
       </c>
     </row>
@@ -27371,24 +27371,24 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Росзапчасть</t>
+          <t>УАЗ Автоград</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>316000350107602</t>
+          <t>3160-00-3501076-02</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
+          <t>ОАО УАЗ</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
           <t>УАЗ</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>УАЗ</t>
-        </is>
-      </c>
       <c r="I129" t="inlineStr">
         <is>
           <t>оригинал</t>
@@ -27396,27 +27396,27 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Диск переднего тормоза 3160</t>
+          <t>Диск тормозной передний УАЗ  ОАО "УАЗ" **</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>ШТ</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1</v>
+        <v>278</v>
       </c>
       <c r="M129" s="10" t="n">
-        <v>19800</v>
+        <v>1950</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>KZT</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="O129" s="3" t="n">
-        <v>19800</v>
+        <v>10432.5</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr">
         <is>
-          <t>Лист_1, строка 2802</t>
+          <t>По алфавиту, строка 2467</t>
         </is>
       </c>
     </row>
@@ -38057,17 +38057,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>УАЗ Автоград: Вкладыши шатунные 1 25 УАЗ "ЗМЗ" ***** [24-1000104-261; ОАО ЗМЗ] — 1 012 ₸ (сходство 100%)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>УАЗ Автоград: Вкладыши шатунные 0 25 УАЗ ** [24-1000104-ВР; Дайдо Металл Русь (Заволжье)] — 4 919 ₸ (сходство 100%)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>УАЗ Автоград: Вкладыши шатунные 1 25 УАЗ***** [24-1000104-ИР; Дайдо Металл Русь (Заволжье)] — 4 730 ₸ (сходство 100%)</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>УАЗ Автоград: Вкладыши шатунные 0 25 ЗМЗ-406 ** [406.1000104-20; Дайдо Металл Русь (Заволжье)] — 6 463 ₸ (сходство 100%)</t>
         </is>
       </c>
     </row>
@@ -38113,7 +38113,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Росзапчасть: Втулка шатуна 130 [130-1004052; ЗИЛ] — 300 ₸ (сходство 100%)</t>
+          <t>УАЗ Автоград: Втулка шатуна ЗМЗ 405-409 (min 4) * [406.1004052-10; ОАО ЗМЗ] — 1 846 ₸ (сходство 100%)</t>
         </is>
       </c>
     </row>
@@ -39502,7 +39502,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Росзапчасть: Корпус поворотного кулака левый 3163 [316200230404195; УАЗ] — 55 000 ₸ (сходство 100%)</t>
+          <t>Росзапчасть: Корпус поворотного кулака левый 3741 [374100230404195; УАЗ] — 75 900 ₸ (сходство 100%)</t>
         </is>
       </c>
     </row>
@@ -43787,7 +43787,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Росзапчасть: Полумуфта ведущая привода ТНВД ведущая дв.542 Г-3309  4301 [542-1029032; ГАЗ] — 6 600 ₸ (сходство 71%)</t>
+          <t>Росзапчасть: Пружина натяжителя ремня привода ТНВД дв.514 ЗМЗ [514-1111110; ЗМЗ] — 450 ₸ (сходство 71%)</t>
         </is>
       </c>
     </row>
@@ -43837,7 +43837,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Росзапчасть: Редуктор заднего моста 53  (6*37) [53-2402010-11; ГАЗ] — 434 500 ₸ (сходство 74%)</t>
+          <t>Росзапчасть: Редуктор заднего моста 7*37 [4331-2402010; ЗМЗ] — 286 000 ₸ (сходство 74%)</t>
         </is>
       </c>
     </row>
@@ -44233,7 +44233,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>УАЗ Автоград: Сальник клапана 4СТ90 (1шт) [2.51.186; ANDORIA] — 2 097 ₸ (сходство 100%)</t>
+          <t>УАЗ Автоград: Сальник клапана ЗМЗ-402 (1 шт) ВЭЛКОНТ(min 8) * [4021.1007026; ОАО ЗМЗ] — 348 ₸ (сходство 100%)</t>
         </is>
       </c>
     </row>
@@ -44279,7 +44279,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>УАЗ Автоград: Сальник клапана 4СТ90 (1шт) [2.51.186; ANDORIA] — 2 097 ₸ (сходство 100%)</t>
+          <t>УАЗ Автоград: Сальник клапана ЗМЗ-402 (1 шт) ВЭЛКОНТ(min 8) * [4021.1007026; ОАО ЗМЗ] — 348 ₸ (сходство 100%)</t>
         </is>
       </c>
     </row>
@@ -44325,7 +44325,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>УАЗ Автоград: Сальник клапана 4СТ90 (1шт) [2.51.186; ANDORIA] — 2 097 ₸ (сходство 100%)</t>
+          <t>УАЗ Автоград: Сальник клапана ЗМЗ-402 (1 шт) ВЭЛКОНТ(min 8) * [4021.1007026; ОАО ЗМЗ] — 348 ₸ (сходство 100%)</t>
         </is>
       </c>
     </row>
@@ -44557,12 +44557,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
+          <t>Росзапчасть: Ремкомплект ступицы колеса [374100310300700; УАЗ] — 7 400 ₸ (сходство 100%)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
           <t>Росзапчасть: Болт ступицы колеса задний [3302-3104018; ГАЗ] — 800 ₸ (сходство 100%)</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Росзапчасть: Ремкомплект ступицы колеса [374100310300700; УАЗ] — 7 400 ₸ (сходство 100%)</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -48545,7 +48545,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>нет, только ГАЗ/УАЗ</t>
+          <t>нет, только ГАЗ/УАЗ (с ЗМЗ и УМЗ)</t>
         </is>
       </c>
     </row>

--- a/result/price_comparison_2026-10-12.xlsx
+++ b/result/price_comparison_2026-10-12.xlsx
@@ -1987,7 +1987,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>452-00-1702024-02</t>
+          <t>0452-00-1702024-02</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>3151-3502040</t>
+          <t>3151-00--3502040-00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>3160-3506033</t>
+          <t>3160-00-3506033-00</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>69-2401055</t>
+          <t>0069-00-2401055-00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -17212,12 +17212,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>452-00-1702024-02</t>
+          <t>0452-00-1702024-02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ 4</t>
+          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Вилка 1-2 передачи 452 4-х синх. КПП</t>
+          <t>Вилка 1-2 передачи 452  с/о**</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -17237,10 +17237,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>1040</v>
+        <v>1066</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -17248,11 +17248,11 @@
         </is>
       </c>
       <c r="O15" s="3" t="n">
-        <v>5564</v>
+        <v>5703.1</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>артикул</t>
+          <t>артикул без точек, тире и кода модификации</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -17267,12 +17267,12 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ 4»</t>
+          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ»</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 1247</t>
+          <t>По алфавиту, строка 1246</t>
         </is>
       </c>
     </row>
@@ -17302,12 +17302,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0452-00-1702024-02</t>
+          <t>452-00-1702024-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ</t>
+          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ 4</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Вилка 1-2 передачи 452  с/о**</t>
+          <t>Вилка 1-2 передачи 452 4-х синх. КПП</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -17327,10 +17327,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>1066</v>
+        <v>1040</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -17338,11 +17338,11 @@
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>5703.1</v>
+        <v>5564</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>артикул без точек, тире и кода модификации</t>
+          <t>артикул</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -17357,12 +17357,12 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ»</t>
+          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ 4»</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 1246</t>
+          <t>По алфавиту, строка 1247</t>
         </is>
       </c>
     </row>
@@ -18292,17 +18292,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>3151-3502040</t>
+          <t>3151-00--3502040-00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>FENOX (Беларусь)</t>
+          <t>ExpertDetal</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>FENOX (Беларусь)</t>
+          <t>ExpertDetal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -18312,7 +18312,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Цилиндр колесный задний д.32  ( К3205) Фенокс</t>
+          <t>Цилиндр колесный задний д.25 (М12) ExpertDetal **</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -18321,10 +18321,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="M27" s="10" t="n">
-        <v>1145</v>
+        <v>737.45</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -18332,11 +18332,11 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>6125.75</v>
+        <v>3945.36</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>артикул</t>
+          <t>артикул без точек, тире и кода модификации</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -18352,7 +18352,7 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 11729</t>
+          <t>По алфавиту, строка 11718</t>
         </is>
       </c>
     </row>
@@ -18382,17 +18382,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3151-00--3502040-00</t>
+          <t>3151-00-3502040</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ExpertDetal</t>
+          <t>Виктория-НН</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ExpertDetal</t>
+          <t>Виктория-НН</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -18402,7 +18402,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Цилиндр колесный задний д.25 (М12) ExpertDetal **</t>
+          <t>Цилиндр колесный задний д.25 (М12) Виктория-НН</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -18411,10 +18411,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="M28" s="10" t="n">
-        <v>737.45</v>
+        <v>442.5</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         </is>
       </c>
       <c r="O28" s="3" t="n">
-        <v>3945.36</v>
+        <v>2367.38</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 11718</t>
+          <t>По алфавиту, строка 11719</t>
         </is>
       </c>
     </row>
@@ -18472,17 +18472,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3151-00-3502040</t>
+          <t>3151-00-3502040-00</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Виктория-НН</t>
+          <t>FENOX (Беларусь)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Виктория-НН</t>
+          <t>FENOX (Беларусь)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -18492,7 +18492,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Цилиндр колесный задний д.25 (М12) Виктория-НН</t>
+          <t>Цилиндр колесный задний д.25 Фенокс (К2561)</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -18501,10 +18501,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="M29" s="10" t="n">
-        <v>442.5</v>
+        <v>924.5599999999999</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>2367.38</v>
+        <v>4946.4</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 11719</t>
+          <t>По алфавиту, строка 11721</t>
         </is>
       </c>
     </row>
@@ -18562,7 +18562,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3151-00-3502040-00</t>
+          <t>3151-3502040</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -18582,7 +18582,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Цилиндр колесный задний д.25 Фенокс (К2561)</t>
+          <t>Цилиндр колесный задний д.32  ( К3205) Фенокс</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -18591,10 +18591,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M30" s="10" t="n">
-        <v>924.5599999999999</v>
+        <v>1145</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -18602,11 +18602,11 @@
         </is>
       </c>
       <c r="O30" s="3" t="n">
-        <v>4946.4</v>
+        <v>6125.75</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>артикул без точек, тире и кода модификации</t>
+          <t>артикул</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -18622,7 +18622,7 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 11721</t>
+          <t>По алфавиту, строка 11729</t>
         </is>
       </c>
     </row>
@@ -18647,22 +18647,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Росзапчасть</t>
+          <t>УАЗ Автоград</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>469-3502040</t>
+          <t>469-00-3502040-00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>АВТОМАГНАТ</t>
+          <t>ExpertDetal</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>АВТОМАГНАТ</t>
+          <t>ExpertDetal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -18672,31 +18672,31 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Цилиндр тормозной колесный УАЗ-469 (d=32/12) (02-071) 469-3502040</t>
+          <t>Цилиндр колесный задний д.32 Expert Detal **</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>ШТ</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="M31" s="10" t="n">
-        <v>3850</v>
+        <v>751.84</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>KZT</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="O31" s="3" t="n">
-        <v>3850</v>
+        <v>4022.34</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>артикул</t>
+          <t>артикул без точек, тире и кода модификации</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -18712,7 +18712,7 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Лист_1, строка 13051</t>
+          <t>По алфавиту, строка 11735</t>
         </is>
       </c>
     </row>
@@ -18747,12 +18747,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ExpertDetal</t>
+          <t>Виктория-НН</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ExpertDetal</t>
+          <t>Виктория-НН</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -18762,7 +18762,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Цилиндр колесный задний д.32 Expert Detal **</t>
+          <t>Цилиндр колесный задний д.32 Виктория-НН</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -18771,10 +18771,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="M32" s="10" t="n">
-        <v>751.84</v>
+        <v>427.5</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         </is>
       </c>
       <c r="O32" s="3" t="n">
-        <v>4022.34</v>
+        <v>2287.12</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 11735</t>
+          <t>По алфавиту, строка 11736</t>
         </is>
       </c>
     </row>
@@ -18827,22 +18827,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>УАЗ Автоград</t>
+          <t>Росзапчасть</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>469-00-3502040-00</t>
+          <t>469-3502040</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Виктория-НН</t>
+          <t>АВТОМАГНАТ</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Виктория-НН</t>
+          <t>АВТОМАГНАТ</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -18852,31 +18852,31 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Цилиндр колесный задний д.32 Виктория-НН</t>
+          <t>Цилиндр тормозной колесный УАЗ-469 (d=32/12) (02-071) 469-3502040</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>ШТ</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="M33" s="10" t="n">
-        <v>427.5</v>
+        <v>3850</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>KZT</t>
         </is>
       </c>
       <c r="O33" s="3" t="n">
-        <v>2287.12</v>
+        <v>3850</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>артикул без точек, тире и кода модификации</t>
+          <t>артикул</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -18892,7 +18892,7 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 11736</t>
+          <t>Лист_1, строка 13051</t>
         </is>
       </c>
     </row>
@@ -19094,17 +19094,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Росзапчасть</t>
+          <t>УАЗ Автоград</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3151-3510178</t>
+          <t>3151-00-3510178-00</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ульяновск</t>
+          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ 3</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -19115,31 +19115,31 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Клапан обратный вакуумного усилителя УАЗ-452,3151 алюм</t>
+          <t>Клапан обратный вакуума в сборе (пластик) старого образца.  **</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>ШТ</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>222</v>
       </c>
       <c r="M36" s="10" t="n">
-        <v>1450</v>
+        <v>139</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>KZT</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="O36" s="3" t="n">
-        <v>1450</v>
+        <v>743.65</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>артикул</t>
+          <t>артикул без точек, тире и кода модификации</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -19154,12 +19154,12 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>производитель в прайсе: «Ульяновск»</t>
+          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ 3»</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>Лист_1, строка 3548</t>
+          <t>По алфавиту, строка 3502</t>
         </is>
       </c>
     </row>
@@ -19205,7 +19205,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Клапан обратный вакуумного усилителя УАЗ-452,3151 пласт</t>
+          <t>Клапан обратный вакуумного усилителя УАЗ-452,3151 алюм</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -19214,7 +19214,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M37" s="10" t="n">
         <v>1450</v>
@@ -19249,7 +19249,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>Лист_1, строка 3549</t>
+          <t>Лист_1, строка 3548</t>
         </is>
       </c>
     </row>
@@ -19274,17 +19274,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>УАЗ Автоград</t>
+          <t>Росзапчасть</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3151-00-3510178-00</t>
+          <t>3151-3510178</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ 3</t>
+          <t>Ульяновск</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -19295,31 +19295,31 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Клапан обратный вакуума в сборе (пластик) старого образца.  **</t>
+          <t>Клапан обратный вакуумного усилителя УАЗ-452,3151 пласт</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>ШТ</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>222</v>
+        <v>2</v>
       </c>
       <c r="M38" s="10" t="n">
-        <v>139</v>
+        <v>1450</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>KZT</t>
         </is>
       </c>
       <c r="O38" s="3" t="n">
-        <v>743.65</v>
+        <v>1450</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>артикул без точек, тире и кода модификации</t>
+          <t>артикул</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -19334,12 +19334,12 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ 3»</t>
+          <t>производитель в прайсе: «Ульяновск»</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 3502</t>
+          <t>Лист_1, строка 3549</t>
         </is>
       </c>
     </row>
@@ -20785,49 +20785,48 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Росзапчасть</t>
+          <t>УАЗ Автоград</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>045100170310331</t>
+          <t>0451-00-1703103-31</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>УАЗ</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>УАЗ</t>
-        </is>
-      </c>
+          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ 3</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>оригинал</t>
+          <t>не указан</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Кронштейн промежуточных рычагов УАЗ (курица большая)</t>
+          <t>Кронштейн промежуточных рычагов в сб. (курица большая) КООП  **</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>ШТ</t>
-        </is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>70</v>
       </c>
       <c r="M55" s="10" t="n">
-        <v>13200</v>
+        <v>845</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>KZT</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="O55" s="3" t="n">
-        <v>13200</v>
+        <v>4520.75</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -20836,14 +20835,22 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>производитель не указан или указан не бренд</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ 3»</t>
+        </is>
+      </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>Лист_1, строка 5376</t>
+          <t>По алфавиту, строка 4757</t>
         </is>
       </c>
     </row>
@@ -20868,48 +20875,49 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>УАЗ Автоград</t>
+          <t>Росзапчасть</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0451-00-1703103-31</t>
+          <t>045100170310331</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ 3</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>УАЗ</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>УАЗ</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>не указан</t>
+          <t>оригинал</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Кронштейн промежуточных рычагов в сб. (курица большая) КООП  **</t>
+          <t>Кронштейн промежуточных рычагов УАЗ (курица большая)</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>70</v>
+          <t>ШТ</t>
+        </is>
       </c>
       <c r="M56" s="10" t="n">
-        <v>845</v>
+        <v>13200</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>KZT</t>
         </is>
       </c>
       <c r="O56" s="3" t="n">
-        <v>4520.75</v>
+        <v>13200</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -20918,22 +20926,14 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>производитель не указан или указан не бренд</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ 3»</t>
-        </is>
-      </c>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 4757</t>
+          <t>Лист_1, строка 5376</t>
         </is>
       </c>
     </row>
@@ -26394,17 +26394,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>3741-3103038</t>
+          <t>3741-00-3103038-00</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>ESPRA</t>
+          <t>ROSTECO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>ESPRA</t>
+          <t>ROSTECO</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26414,7 +26414,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Сальник ступицы 60х85х10 колеса с пружиной в сб.(материал FKM) ЕО 1731</t>
+          <t>Сальник ступицы 60х85х10 колеса с пружиной в сб. РОСТЕКО</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -26423,10 +26423,10 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>17</v>
+        <v>588</v>
       </c>
       <c r="M118" s="10" t="n">
-        <v>365.91</v>
+        <v>121.7</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
@@ -26434,11 +26434,11 @@
         </is>
       </c>
       <c r="O118" s="3" t="n">
-        <v>1957.62</v>
+        <v>651.1</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>артикул</t>
+          <t>артикул без точек, тире и кода модификации</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -26454,7 +26454,7 @@
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 9464</t>
+          <t>По алфавиту, строка 9461</t>
         </is>
       </c>
     </row>
@@ -26479,52 +26479,56 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Росзапчасть</t>
+          <t>УАЗ Автоград</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>3741-3103038</t>
+          <t>3741-00-3103038-00</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Чайковский</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
+          <t>NAK (Тайвань)</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>NAK (Тайвань)</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>не указан</t>
+          <t>аналог</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Сальник 60*85 ступицы</t>
+          <t>Сальник ступицы 60х85х10 колеса с пружиной в сб."NAK" (Тайвань)</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>ШТ</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>201.5</v>
+        <v>2497</v>
       </c>
       <c r="M119" s="10" t="n">
-        <v>700</v>
+        <v>136</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>KZT</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="O119" s="3" t="n">
-        <v>700</v>
+        <v>727.6</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>артикул</t>
+          <t>артикул без точек, тире и кода модификации</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -26534,17 +26538,13 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>производитель не указан или указан не бренд</t>
-        </is>
-      </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>производитель в прайсе: «Чайковский»</t>
-        </is>
-      </c>
+          <t>аналог, не ГАЗ/УАЗ</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr">
         <is>
-          <t>Лист_1, строка 10686</t>
+          <t>По алфавиту, строка 9462</t>
         </is>
       </c>
     </row>
@@ -26569,22 +26569,22 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Росзапчасть</t>
+          <t>УАЗ Автоград</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>3741-3103038</t>
+          <t>3741-00-3103038-00</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>ПтиМаш</t>
+          <t>TRIALLI</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>ПтиМаш</t>
+          <t>TRIALLI</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -26594,31 +26594,31 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Сальник 60*85*10 ступицы чёрный</t>
+          <t>Сальник ступицы 60х85х10 колеса с пружиной в сб.(PS 601) TRIALLI (16)</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>ШТ</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M120" s="10" t="n">
-        <v>350</v>
+        <v>245.5</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>KZT</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="O120" s="3" t="n">
-        <v>350</v>
+        <v>1313.42</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>артикул</t>
+          <t>артикул без точек, тире и кода модификации</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -26634,7 +26634,7 @@
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr">
         <is>
-          <t>Лист_1, строка 10689</t>
+          <t>По алфавиту, строка 9463</t>
         </is>
       </c>
     </row>
@@ -26664,17 +26664,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>3741-00-3103038-00</t>
+          <t>3741-3103038</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>ROSTECO</t>
+          <t>ESPRA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>ROSTECO</t>
+          <t>ESPRA</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Сальник ступицы 60х85х10 колеса с пружиной в сб. РОСТЕКО</t>
+          <t>Сальник ступицы 60х85х10 колеса с пружиной в сб.(материал FKM) ЕО 1731</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -26693,10 +26693,10 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>588</v>
+        <v>17</v>
       </c>
       <c r="M121" s="10" t="n">
-        <v>121.7</v>
+        <v>365.91</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -26704,11 +26704,11 @@
         </is>
       </c>
       <c r="O121" s="3" t="n">
-        <v>651.1</v>
+        <v>1957.62</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>артикул без точек, тире и кода модификации</t>
+          <t>артикул</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -26724,7 +26724,7 @@
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 9461</t>
+          <t>По алфавиту, строка 9464</t>
         </is>
       </c>
     </row>
@@ -26759,12 +26759,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>NAK (Тайвань)</t>
+          <t>УРАЛЭЛАСТОМЕР (Чайковский)</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>NAK (Тайвань)</t>
+          <t>УРАЛЭЛАСТОМЕР (Чайковский)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -26774,7 +26774,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Сальник ступицы 60х85х10 колеса с пружиной в сб."NAK" (Тайвань)</t>
+          <t>Сальник ступицы 60х85х10 колеса с пружиной в сб.(уп.20)</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -26783,10 +26783,10 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2497</v>
+        <v>262</v>
       </c>
       <c r="M122" s="10" t="n">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         </is>
       </c>
       <c r="O122" s="3" t="n">
-        <v>727.6</v>
+        <v>235.4</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 9462</t>
+          <t>По алфавиту, строка 9466</t>
         </is>
       </c>
     </row>
@@ -26839,56 +26839,52 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>УАЗ Автоград</t>
+          <t>Росзапчасть</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>3741-00-3103038-00</t>
+          <t>3741-3103038</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>TRIALLI</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>TRIALLI</t>
-        </is>
-      </c>
+          <t>Чайковский</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>аналог</t>
+          <t>не указан</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Сальник ступицы 60х85х10 колеса с пружиной в сб.(PS 601) TRIALLI (16)</t>
+          <t>Сальник 60*85 ступицы</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>ШТ</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>17</v>
+        <v>201.5</v>
       </c>
       <c r="M123" s="10" t="n">
-        <v>245.5</v>
+        <v>700</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>KZT</t>
         </is>
       </c>
       <c r="O123" s="3" t="n">
-        <v>1313.42</v>
+        <v>700</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>артикул без точек, тире и кода модификации</t>
+          <t>артикул</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -26898,13 +26894,17 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>аналог, не ГАЗ/УАЗ</t>
-        </is>
-      </c>
-      <c r="S123" t="inlineStr"/>
+          <t>производитель не указан или указан не бренд</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>производитель в прайсе: «Чайковский»</t>
+        </is>
+      </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 9463</t>
+          <t>Лист_1, строка 10686</t>
         </is>
       </c>
     </row>
@@ -26929,22 +26929,22 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>УАЗ Автоград</t>
+          <t>Росзапчасть</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>3741-00-3103038-00</t>
+          <t>3741-3103038</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>УРАЛЭЛАСТОМЕР (Чайковский)</t>
+          <t>ПтиМаш</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>УРАЛЭЛАСТОМЕР (Чайковский)</t>
+          <t>ПтиМаш</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -26954,31 +26954,31 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Сальник ступицы 60х85х10 колеса с пружиной в сб.(уп.20)</t>
+          <t>Сальник 60*85*10 ступицы чёрный</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>ШТ</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>262</v>
+        <v>20</v>
       </c>
       <c r="M124" s="10" t="n">
-        <v>44</v>
+        <v>350</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>KZT</t>
         </is>
       </c>
       <c r="O124" s="3" t="n">
-        <v>235.4</v>
+        <v>350</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>артикул без точек, тире и кода модификации</t>
+          <t>артикул</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
@@ -26994,7 +26994,7 @@
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 9466</t>
+          <t>Лист_1, строка 10689</t>
         </is>
       </c>
     </row>
@@ -27285,24 +27285,24 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Росзапчасть</t>
+          <t>УАЗ Автоград</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>316000350107602</t>
+          <t>3160-00-3501076-02</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
+          <t>ОАО УАЗ</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
           <t>УАЗ</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>УАЗ</t>
-        </is>
-      </c>
       <c r="I128" t="inlineStr">
         <is>
           <t>оригинал</t>
@@ -27310,27 +27310,27 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Диск переднего тормоза 3160</t>
+          <t>Диск тормозной передний УАЗ  ОАО "УАЗ" **</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>ШТ</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1</v>
+        <v>278</v>
       </c>
       <c r="M128" s="10" t="n">
-        <v>19800</v>
+        <v>1950</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>KZT</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="O128" s="3" t="n">
-        <v>19800</v>
+        <v>10432.5</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr">
         <is>
-          <t>Лист_1, строка 2802</t>
+          <t>По алфавиту, строка 2467</t>
         </is>
       </c>
     </row>
@@ -27371,17 +27371,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>УАЗ Автоград</t>
+          <t>Росзапчасть</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>3160-00-3501076-02</t>
+          <t>316000350107602</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>ОАО УАЗ</t>
+          <t>УАЗ</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -27396,27 +27396,27 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Диск тормозной передний УАЗ  ОАО "УАЗ" **</t>
+          <t>Диск переднего тормоза 3160</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>ШТ</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>278</v>
+        <v>1</v>
       </c>
       <c r="M129" s="10" t="n">
-        <v>1950</v>
+        <v>19800</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>KZT</t>
         </is>
       </c>
       <c r="O129" s="3" t="n">
-        <v>10432.5</v>
+        <v>19800</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 2467</t>
+          <t>Лист_1, строка 2802</t>
         </is>
       </c>
     </row>
@@ -27716,17 +27716,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Росзапчасть</t>
+          <t>УАЗ Автоград</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>3160-3506033</t>
+          <t>3160-00-3506033-00</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ульяновск</t>
+          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -27737,31 +27737,28 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Тройник турбопровода к задним тормозам УАЗ-31519 Хантер,3163 Патриот</t>
+          <t>Тройник трубопровода к задним гидровлическим тормозам **</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>ШТ</t>
-        </is>
-      </c>
-      <c r="L133" t="n">
-        <v>1</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="M133" s="10" t="n">
-        <v>900</v>
+        <v>260</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>KZT</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="O133" s="3" t="n">
-        <v>900</v>
+        <v>1391</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>артикул</t>
+          <t>артикул без точек, тире и кода модификации</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -27776,12 +27773,12 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>производитель в прайсе: «Ульяновск»</t>
+          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ»</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>Лист_1, строка 11586</t>
+          <t>По алфавиту, строка 10287</t>
         </is>
       </c>
     </row>
@@ -27806,17 +27803,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>УАЗ Автоград</t>
+          <t>Росзапчасть</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>3160-00-3506033-00</t>
+          <t>3160-3506033</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ</t>
+          <t>Ульяновск</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
@@ -27827,28 +27824,31 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Тройник трубопровода к задним гидровлическим тормозам **</t>
+          <t>Тройник турбопровода к задним тормозам УАЗ-31519 Хантер,3163 Патриот</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
+          <t>ШТ</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>1</v>
       </c>
       <c r="M134" s="10" t="n">
-        <v>260</v>
+        <v>900</v>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>KZT</t>
         </is>
       </c>
       <c r="O134" s="3" t="n">
-        <v>1391</v>
+        <v>900</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>артикул без точек, тире и кода модификации</t>
+          <t>артикул</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -27863,12 +27863,12 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ»</t>
+          <t>производитель в прайсе: «Ульяновск»</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 10287</t>
+          <t>Лист_1, строка 11586</t>
         </is>
       </c>
     </row>
@@ -28078,27 +28078,27 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69-1802075-01</t>
+          <t>0069-00-1802075-01</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Виктория-НН</t>
+          <t>ОАО УАЗ</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Виктория-НН</t>
+          <t>УАЗ</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>аналог</t>
+          <t>оригинал</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Фланец РК  вала привода зад.моста в сборе с резьбой Виктория-НН</t>
+          <t>Фланец РК  вала привода зад.моста в сборе с резьбой (ОАО УАЗ)**</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -28107,10 +28107,10 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>495</v>
+        <v>95</v>
       </c>
       <c r="M137" s="10" t="n">
-        <v>865.2</v>
+        <v>998</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
@@ -28118,27 +28118,23 @@
         </is>
       </c>
       <c r="O137" s="3" t="n">
-        <v>4628.82</v>
+        <v>5339.3</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>артикул</t>
+          <t>артикул без точек, тире и кода модификации</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="R137" t="inlineStr">
-        <is>
-          <t>аналог, не ГАЗ/УАЗ</t>
-        </is>
-      </c>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 11460</t>
+          <t>По алфавиту, строка 11459</t>
         </is>
       </c>
     </row>
@@ -28168,27 +28164,27 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>0069-00-1802075-01</t>
+          <t>69-1802075-01</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>ОАО УАЗ</t>
+          <t>Виктория-НН</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>УАЗ</t>
+          <t>Виктория-НН</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>оригинал</t>
+          <t>аналог</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Фланец РК  вала привода зад.моста в сборе с резьбой (ОАО УАЗ)**</t>
+          <t>Фланец РК  вала привода зад.моста в сборе с резьбой Виктория-НН</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -28197,10 +28193,10 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>95</v>
+        <v>495</v>
       </c>
       <c r="M138" s="10" t="n">
-        <v>998</v>
+        <v>865.2</v>
       </c>
       <c r="N138" t="inlineStr">
         <is>
@@ -28208,23 +28204,27 @@
         </is>
       </c>
       <c r="O138" s="3" t="n">
-        <v>5339.3</v>
+        <v>4628.82</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>артикул без точек, тире и кода модификации</t>
+          <t>артикул</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="R138" t="inlineStr"/>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>аналог, не ГАЗ/УАЗ</t>
+        </is>
+      </c>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 11459</t>
+          <t>По алфавиту, строка 11460</t>
         </is>
       </c>
     </row>
@@ -28337,27 +28337,27 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69-1802043-01</t>
+          <t>0069-00-1802043-01</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Виктория-НН</t>
+          <t>ОАО УАЗ</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Виктория-НН</t>
+          <t>УАЗ</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>аналог</t>
+          <t>оригинал</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Фланец РК переднего моста в сборе Виктория-НН</t>
+          <t>Фланец РК переднего моста в сборе ( ОАО УАЗ)**</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -28366,10 +28366,10 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1313</v>
+        <v>119</v>
       </c>
       <c r="M140" s="10" t="n">
-        <v>777.65</v>
+        <v>998</v>
       </c>
       <c r="N140" t="inlineStr">
         <is>
@@ -28377,27 +28377,23 @@
         </is>
       </c>
       <c r="O140" s="3" t="n">
-        <v>4160.43</v>
+        <v>5339.3</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>артикул</t>
+          <t>артикул без точек, тире и кода модификации</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>аналог, не ГАЗ/УАЗ</t>
-        </is>
-      </c>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 11463</t>
+          <t>По алфавиту, строка 11462</t>
         </is>
       </c>
     </row>
@@ -28422,7 +28418,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Росзапчасть</t>
+          <t>УАЗ Автоград</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -28432,12 +28428,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>АВТОМАГНАТ</t>
+          <t>Виктория-НН</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>АВТОМАГНАТ</t>
+          <t>Виктория-НН</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -28447,27 +28443,27 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Фланец УАЗ коробки раздаточной передний</t>
+          <t>Фланец РК переднего моста в сборе Виктория-НН</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>ШТ</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2</v>
+        <v>1313</v>
       </c>
       <c r="M141" s="10" t="n">
-        <v>6300</v>
+        <v>777.65</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>KZT</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="O141" s="3" t="n">
-        <v>6300</v>
+        <v>4160.43</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
@@ -28487,7 +28483,7 @@
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr">
         <is>
-          <t>Лист_1, строка 12617</t>
+          <t>По алфавиту, строка 11463</t>
         </is>
       </c>
     </row>
@@ -28512,17 +28508,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>УАЗ Автоград</t>
+          <t>Росзапчасть</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>0069-00-1802043-01</t>
+          <t>006900180204301</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>ОАО УАЗ</t>
+          <t>УАЗ</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -28537,27 +28533,27 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Фланец РК переднего моста в сборе ( ОАО УАЗ)**</t>
+          <t>ФЛАНЕЦ ПРОМЕЖУТОЧНОГО ВАЛА</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>ШТ</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="M142" s="10" t="n">
-        <v>998</v>
+        <v>9900</v>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>KZT</t>
         </is>
       </c>
       <c r="O142" s="3" t="n">
-        <v>5339.3</v>
+        <v>9900</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
@@ -28573,7 +28569,7 @@
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 11462</t>
+          <t>Лист_1, строка 12610</t>
         </is>
       </c>
     </row>
@@ -28603,27 +28599,27 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>006900180204301</t>
+          <t>69-1802043-01</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>УАЗ</t>
+          <t>АВТОМАГНАТ</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>УАЗ</t>
+          <t>АВТОМАГНАТ</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>оригинал</t>
+          <t>аналог</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>ФЛАНЕЦ ПРОМЕЖУТОЧНОГО ВАЛА</t>
+          <t>Фланец УАЗ коробки раздаточной передний</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -28635,7 +28631,7 @@
         <v>2</v>
       </c>
       <c r="M143" s="10" t="n">
-        <v>9900</v>
+        <v>6300</v>
       </c>
       <c r="N143" t="inlineStr">
         <is>
@@ -28643,23 +28639,27 @@
         </is>
       </c>
       <c r="O143" s="3" t="n">
-        <v>9900</v>
+        <v>6300</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>артикул без точек, тире и кода модификации</t>
+          <t>артикул</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="R143" t="inlineStr"/>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>аналог, не ГАЗ/УАЗ</t>
+        </is>
+      </c>
       <c r="S143" t="inlineStr"/>
       <c r="T143" t="inlineStr">
         <is>
-          <t>Лист_1, строка 12610</t>
+          <t>Лист_1, строка 12617</t>
         </is>
       </c>
     </row>
@@ -28858,49 +28858,52 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Росзапчасть</t>
+          <t>УАЗ Автоград</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>006900230408000</t>
+          <t>0069-00-2304080-00</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>УАЗ</t>
+          <t>ИП Кузнецов Н.М. (Ульяновск)</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>УАЗ</t>
+          <t>ИП Кузнецов Н.М. (Ульяновск)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>оригинал</t>
+          <t>аналог</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>ЦАПФА ПОВОРОТНОГО КУЛАКА (ДЛЯ А/М УАЗ ПАТРИОТ, ХАНТЕР,  СГР С МОСТАМИ СПАЙСЕР, ХАНТЕР, СГР С МОСТАМ</t>
+          <t>Цапфа поворотного кулака переднего моста в сб  / АВТОГИДРАВЛИКА/</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>ШТ</t>
-        </is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>21</v>
       </c>
       <c r="M146" s="10" t="n">
-        <v>40700</v>
+        <v>3858.4</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>KZT</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="O146" s="3" t="n">
-        <v>40700</v>
+        <v>20642.44</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
@@ -28909,14 +28912,18 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="R146" t="inlineStr"/>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>аналог, не ГАЗ/УАЗ</t>
+        </is>
+      </c>
       <c r="S146" t="inlineStr"/>
       <c r="T146" t="inlineStr">
         <is>
-          <t>Лист_1, строка 12846</t>
+          <t>По алфавиту, строка 11610</t>
         </is>
       </c>
     </row>
@@ -28951,12 +28958,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>ИП Кузнецов Н.М. (Ульяновск)</t>
+          <t>АВТОМАГНАТ</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>ИП Кузнецов Н.М. (Ульяновск)</t>
+          <t>АВТОМАГНАТ</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -28966,7 +28973,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Цапфа поворотного кулака переднего моста в сб  / АВТОГИДРАВЛИКА/</t>
+          <t>Цапфа поворотного кулака переднего моста в сб  АВТОМАГНАТ/новинка/</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -28975,10 +28982,10 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="M147" s="10" t="n">
-        <v>3858.4</v>
+        <v>1901</v>
       </c>
       <c r="N147" t="inlineStr">
         <is>
@@ -28986,7 +28993,7 @@
         </is>
       </c>
       <c r="O147" s="3" t="n">
-        <v>20642.44</v>
+        <v>10170.35</v>
       </c>
       <c r="P147" t="inlineStr">
         <is>
@@ -29006,7 +29013,7 @@
       <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 11610</t>
+          <t>По алфавиту, строка 11611</t>
         </is>
       </c>
     </row>
@@ -29041,22 +29048,18 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>АВТОМАГНАТ</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>АВТОМАГНАТ</t>
-        </is>
-      </c>
+          <t>ПРОЧИЕ ПОСТАВЩИКИ</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
-          <t>аналог</t>
+          <t>не указан</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Цапфа поворотного кулака переднего моста в сб  АВТОМАГНАТ/новинка/</t>
+          <t>Цапфа поворотного кулака переднего моста в сб  ТРОФИ</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -29065,10 +29068,10 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>298</v>
+        <v>174</v>
       </c>
       <c r="M148" s="10" t="n">
-        <v>1901</v>
+        <v>2401</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>
@@ -29076,7 +29079,7 @@
         </is>
       </c>
       <c r="O148" s="3" t="n">
-        <v>10170.35</v>
+        <v>12845.35</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
@@ -29090,13 +29093,17 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>аналог, не ГАЗ/УАЗ</t>
-        </is>
-      </c>
-      <c r="S148" t="inlineStr"/>
+          <t>производитель не указан или указан не бренд</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>производитель в прайсе: «ПРОЧИЕ ПОСТАВЩИКИ»</t>
+        </is>
+      </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 11611</t>
+          <t>По алфавиту, строка 11612</t>
         </is>
       </c>
     </row>
@@ -29131,18 +29138,22 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>ПРОЧИЕ ПОСТАВЩИКИ</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr"/>
+          <t>ОАО УАЗ</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>УАЗ</t>
+        </is>
+      </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>не указан</t>
+          <t>оригинал</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Цапфа поворотного кулака переднего моста в сб  ТРОФИ</t>
+          <t>Цапфа поворотного кулака переднего моста в сб ОАО УАЗ **</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -29151,10 +29162,10 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>174</v>
+        <v>38</v>
       </c>
       <c r="M149" s="10" t="n">
-        <v>2401</v>
+        <v>2999</v>
       </c>
       <c r="N149" t="inlineStr">
         <is>
@@ -29162,7 +29173,7 @@
         </is>
       </c>
       <c r="O149" s="3" t="n">
-        <v>12845.35</v>
+        <v>16044.65</v>
       </c>
       <c r="P149" t="inlineStr">
         <is>
@@ -29171,22 +29182,14 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr">
-        <is>
-          <t>производитель не указан или указан не бренд</t>
-        </is>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>производитель в прайсе: «ПРОЧИЕ ПОСТАВЩИКИ»</t>
-        </is>
-      </c>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr"/>
+      <c r="S149" t="inlineStr"/>
       <c r="T149" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 11612</t>
+          <t>По алфавиту, строка 11613</t>
         </is>
       </c>
     </row>
@@ -29221,22 +29224,18 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>ОАО УАЗ</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>УАЗ</t>
-        </is>
-      </c>
+          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ 6</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>оригинал</t>
+          <t>не указан</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Цапфа поворотного кулака переднего моста в сб ОАО УАЗ **</t>
+          <t>Цапфа поворотного кулака переднего моста в сб.  Виктория НН</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -29245,10 +29244,10 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="M150" s="10" t="n">
-        <v>2999</v>
+        <v>2190</v>
       </c>
       <c r="N150" t="inlineStr">
         <is>
@@ -29256,7 +29255,7 @@
         </is>
       </c>
       <c r="O150" s="3" t="n">
-        <v>16044.65</v>
+        <v>11716.5</v>
       </c>
       <c r="P150" t="inlineStr">
         <is>
@@ -29265,14 +29264,22 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr"/>
-      <c r="S150" t="inlineStr"/>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>производитель не указан или указан не бренд</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ 6»</t>
+        </is>
+      </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 11613</t>
+          <t>По алфавиту, строка 11614</t>
         </is>
       </c>
     </row>
@@ -29297,48 +29304,52 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>УАЗ Автоград</t>
+          <t>Росзапчасть</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>0069-00-2304080-00</t>
+          <t>69-2304080</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ 6</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr"/>
+          <t>АВТОМАГНАТ</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>АВТОМАГНАТ</t>
+        </is>
+      </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>не указан</t>
+          <t>аналог</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Цапфа поворотного кулака переднего моста в сб.  Виктория НН</t>
+          <t>Цапфа кулака поворотного в сборе УАЗ-452, 469, 3163</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>ШТ</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="M151" s="10" t="n">
-        <v>2190</v>
+        <v>19500</v>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>KZT</t>
         </is>
       </c>
       <c r="O151" s="3" t="n">
-        <v>11716.5</v>
+        <v>19500</v>
       </c>
       <c r="P151" t="inlineStr">
         <is>
@@ -29352,17 +29363,13 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>производитель не указан или указан не бренд</t>
-        </is>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ 6»</t>
-        </is>
-      </c>
+          <t>аналог, не ГАЗ/УАЗ</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 11614</t>
+          <t>Лист_1, строка 12842</t>
         </is>
       </c>
     </row>
@@ -29392,17 +29399,17 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69-2304080</t>
+          <t>0069-00-2304080-00</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>АВТОМАГНАТ</t>
+          <t>ВАП</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>АВТОМАГНАТ</t>
+          <t>ВАП</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -29412,7 +29419,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Цапфа кулака поворотного в сборе УАЗ-452, 469, 3163</t>
+          <t>Цапфа поворотн кулака 469</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -29421,10 +29428,10 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M152" s="10" t="n">
-        <v>19500</v>
+        <v>14900</v>
       </c>
       <c r="N152" t="inlineStr">
         <is>
@@ -29432,7 +29439,7 @@
         </is>
       </c>
       <c r="O152" s="3" t="n">
-        <v>19500</v>
+        <v>14900</v>
       </c>
       <c r="P152" t="inlineStr">
         <is>
@@ -29452,7 +29459,7 @@
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr">
         <is>
-          <t>Лист_1, строка 12842</t>
+          <t>Лист_1, строка 12845</t>
         </is>
       </c>
     </row>
@@ -29482,27 +29489,27 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>0069-00-2304080-00</t>
+          <t>006900230408000</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>ВАП</t>
+          <t>УАЗ</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>ВАП</t>
+          <t>УАЗ</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>аналог</t>
+          <t>оригинал</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Цапфа поворотн кулака 469</t>
+          <t>ЦАПФА ПОВОРОТНОГО КУЛАКА (ДЛЯ А/М УАЗ ПАТРИОТ, ХАНТЕР,  СГР С МОСТАМИ СПАЙСЕР, ХАНТЕР, СГР С МОСТАМ</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -29510,11 +29517,8 @@
           <t>ШТ</t>
         </is>
       </c>
-      <c r="L153" t="n">
-        <v>12</v>
-      </c>
       <c r="M153" s="10" t="n">
-        <v>14900</v>
+        <v>40700</v>
       </c>
       <c r="N153" t="inlineStr">
         <is>
@@ -29522,7 +29526,7 @@
         </is>
       </c>
       <c r="O153" s="3" t="n">
-        <v>14900</v>
+        <v>40700</v>
       </c>
       <c r="P153" t="inlineStr">
         <is>
@@ -29531,18 +29535,14 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="R153" t="inlineStr">
-        <is>
-          <t>аналог, не ГАЗ/УАЗ</t>
-        </is>
-      </c>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr">
         <is>
-          <t>Лист_1, строка 12845</t>
+          <t>Лист_1, строка 12846</t>
         </is>
       </c>
     </row>
@@ -29567,56 +29567,52 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Росзапчасть</t>
+          <t>УАЗ Автоград</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69-2401055</t>
+          <t>0069-00-2401055-00</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>РЗИ</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>РЗИ</t>
-        </is>
-      </c>
+          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ 3</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
-          <t>аналог</t>
+          <t>не указан</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Шайба ступицы замочная УАЗ(уп. 10 шт)</t>
+          <t>Шайба замочная (ромашка) (min 10)</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>ШТ</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>60</v>
+        <v>4277</v>
       </c>
       <c r="M154" s="10" t="n">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>KZT</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="O154" s="3" t="n">
-        <v>250</v>
+        <v>64.2</v>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>артикул</t>
+          <t>артикул без точек, тире и кода модификации</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
@@ -29626,13 +29622,17 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>аналог, не ГАЗ/УАЗ</t>
-        </is>
-      </c>
-      <c r="S154" t="inlineStr"/>
+          <t>производитель не указан или указан не бренд</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ 3»</t>
+        </is>
+      </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>Лист_1, строка 13182</t>
+          <t>По алфавиту, строка 11908</t>
         </is>
       </c>
     </row>
@@ -29657,52 +29657,56 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>УАЗ Автоград</t>
+          <t>Росзапчасть</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>0069-00-2401055-00</t>
+          <t>69-2401055</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ 3</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr"/>
+          <t>РЗИ</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>РЗИ</t>
+        </is>
+      </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>не указан</t>
+          <t>аналог</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Шайба замочная (ромашка) (min 10)</t>
+          <t>Шайба ступицы замочная УАЗ(уп. 10 шт)</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>ШТ</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>4277</v>
+        <v>60</v>
       </c>
       <c r="M155" s="10" t="n">
-        <v>12</v>
+        <v>250</v>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>KZT</t>
         </is>
       </c>
       <c r="O155" s="3" t="n">
-        <v>64.2</v>
+        <v>250</v>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>артикул без точек, тире и кода модификации</t>
+          <t>артикул</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
@@ -29712,17 +29716,13 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>производитель не указан или указан не бренд</t>
-        </is>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ 3»</t>
-        </is>
-      </c>
+          <t>аналог, не ГАЗ/УАЗ</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 11908</t>
+          <t>Лист_1, строка 13182</t>
         </is>
       </c>
     </row>
@@ -31640,12 +31640,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>452-00-1702024-02</t>
+          <t>0452-00-1702024-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ 4</t>
+          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -31656,7 +31656,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Вилка 1-2 передачи 452 4-х синх. КПП</t>
+          <t>Вилка 1-2 передачи 452  с/о**</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -31665,10 +31665,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>1040</v>
+        <v>1066</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -31676,11 +31676,11 @@
         </is>
       </c>
       <c r="O6" s="3" t="n">
-        <v>5564</v>
+        <v>5703.1</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>артикул</t>
+          <t>артикул без точек, тире и кода модификации</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -31695,12 +31695,12 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ 4»</t>
+          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ»</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 1247</t>
+          <t>По алфавиту, строка 1246</t>
         </is>
       </c>
     </row>
@@ -31730,12 +31730,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0452-00-1702024-02</t>
+          <t>452-00-1702024-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ</t>
+          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ 4</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -31746,7 +31746,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Вилка 1-2 передачи 452  с/о**</t>
+          <t>Вилка 1-2 передачи 452 4-х синх. КПП</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -31755,10 +31755,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>1066</v>
+        <v>1040</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -31766,11 +31766,11 @@
         </is>
       </c>
       <c r="O7" s="3" t="n">
-        <v>5703.1</v>
+        <v>5564</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>артикул без точек, тире и кода модификации</t>
+          <t>артикул</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -31785,12 +31785,12 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ»</t>
+          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ 4»</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 1246</t>
+          <t>По алфавиту, строка 1247</t>
         </is>
       </c>
     </row>
@@ -32364,17 +32364,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Росзапчасть</t>
+          <t>УАЗ Автоград</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3151-3510178</t>
+          <t>3151-00-3510178-00</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ульяновск</t>
+          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ 3</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -32385,31 +32385,31 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Клапан обратный вакуумного усилителя УАЗ-452,3151 алюм</t>
+          <t>Клапан обратный вакуума в сборе (пластик) старого образца.  **</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>ШТ</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>222</v>
       </c>
       <c r="M14" s="10" t="n">
-        <v>1450</v>
+        <v>139</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>KZT</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="O14" s="3" t="n">
-        <v>1450</v>
+        <v>743.65</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>артикул</t>
+          <t>артикул без точек, тире и кода модификации</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -32424,12 +32424,12 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>производитель в прайсе: «Ульяновск»</t>
+          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ 3»</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Лист_1, строка 3548</t>
+          <t>По алфавиту, строка 3502</t>
         </is>
       </c>
     </row>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Клапан обратный вакуумного усилителя УАЗ-452,3151 пласт</t>
+          <t>Клапан обратный вакуумного усилителя УАЗ-452,3151 алюм</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -32484,7 +32484,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M15" s="10" t="n">
         <v>1450</v>
@@ -32519,7 +32519,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Лист_1, строка 3549</t>
+          <t>Лист_1, строка 3548</t>
         </is>
       </c>
     </row>
@@ -32544,17 +32544,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>УАЗ Автоград</t>
+          <t>Росзапчасть</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3151-00-3510178-00</t>
+          <t>3151-3510178</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ 3</t>
+          <t>Ульяновск</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -32565,31 +32565,31 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Клапан обратный вакуума в сборе (пластик) старого образца.  **</t>
+          <t>Клапан обратный вакуумного усилителя УАЗ-452,3151 пласт</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>ШТ</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>222</v>
+        <v>2</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>139</v>
+        <v>1450</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>KZT</t>
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>743.65</v>
+        <v>1450</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>артикул без точек, тире и кода модификации</t>
+          <t>артикул</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -32604,12 +32604,12 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ 3»</t>
+          <t>производитель в прайсе: «Ульяновск»</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 3502</t>
+          <t>Лист_1, строка 3549</t>
         </is>
       </c>
     </row>
@@ -36074,17 +36074,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Росзапчасть</t>
+          <t>УАЗ Автоград</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>3160-3506033</t>
+          <t>3160-00-3506033-00</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ульяновск</t>
+          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -36095,31 +36095,28 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Тройник турбопровода к задним тормозам УАЗ-31519 Хантер,3163 Патриот</t>
+          <t>Тройник трубопровода к задним гидровлическим тормозам **</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>ШТ</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>1</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="M55" s="10" t="n">
-        <v>900</v>
+        <v>260</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>KZT</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="O55" s="3" t="n">
-        <v>900</v>
+        <v>1391</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>артикул</t>
+          <t>артикул без точек, тире и кода модификации</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -36134,12 +36131,12 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>производитель в прайсе: «Ульяновск»</t>
+          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ»</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>Лист_1, строка 11586</t>
+          <t>По алфавиту, строка 10287</t>
         </is>
       </c>
     </row>
@@ -36164,17 +36161,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>УАЗ Автоград</t>
+          <t>Росзапчасть</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>3160-00-3506033-00</t>
+          <t>3160-3506033</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ПРОЧИЕ ПРОИЗВОДИТЕЛИ</t>
+          <t>Ульяновск</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -36185,28 +36182,31 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Тройник трубопровода к задним гидровлическим тормозам **</t>
+          <t>Тройник турбопровода к задним тормозам УАЗ-31519 Хантер,3163 Патриот</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
+          <t>ШТ</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
       </c>
       <c r="M56" s="10" t="n">
-        <v>260</v>
+        <v>900</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>KZT</t>
         </is>
       </c>
       <c r="O56" s="3" t="n">
-        <v>1391</v>
+        <v>900</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>артикул без точек, тире и кода модификации</t>
+          <t>артикул</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -36221,12 +36221,12 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>производитель в прайсе: «ПРОЧИЕ ПРОИЗВОДИТЕЛИ»</t>
+          <t>производитель в прайсе: «Ульяновск»</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>По алфавиту, строка 10287</t>
+          <t>Лист_1, строка 11586</t>
         </is>
       </c>
     </row>
@@ -39502,7 +39502,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Росзапчасть: Корпус поворотного кулака левый 3741 [374100230404195; УАЗ] — 75 900 ₸ (сходство 100%)</t>
+          <t>Росзапчасть: Корпус поворотного кулака левый 3163 [316200230404195; УАЗ] — 55 000 ₸ (сходство 100%)</t>
         </is>
       </c>
     </row>
@@ -42566,7 +42566,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Росзапчасть: Рем комплект гидровакуумного усилителя [3110-3510800; ГАЗ] — 2 200 ₸ (сходство 73%)</t>
+          <t>Росзапчасть: Гидровакуумный усилитель тормозов 2123 [А21R23.3510009; ГАЗ] — 66 000 ₸ (сходство 73%)</t>
         </is>
       </c>
     </row>
@@ -43491,7 +43491,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Росзапчасть: Сальник 55*70*8 коленвала передний без пружины [409060100503400; УАЗ] — 2 200 ₸ (сходство 100%)</t>
+          <t>УАЗ Автоград: Сальник коленвала задний 100х80х10 ОАО "УАЗ" * [0406-20-1005160; ОАО УАЗ] — 3 140 ₸ (сходство 100%)</t>
         </is>
       </c>
     </row>
@@ -43541,7 +43541,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Росзапчасть: Сальник 55*70*8 коленвала передний без пружины [409060100503400; УАЗ] — 2 200 ₸ (сходство 100%)</t>
+          <t>УАЗ Автоград: Сальник коленвала задний 100х80х10 ОАО "УАЗ" * [0406-20-1005160; ОАО УАЗ] — 3 140 ₸ (сходство 100%)</t>
         </is>
       </c>
     </row>
@@ -43591,7 +43591,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Росзапчасть: Сальник 55*70*8 коленвала передний без пружины [409060100503400; УАЗ] — 2 200 ₸ (сходство 100%)</t>
+          <t>УАЗ Автоград: Сальник коленвала задний 100х80х10 ОАО "УАЗ" * [0406-20-1005160; ОАО УАЗ] — 3 140 ₸ (сходство 100%)</t>
         </is>
       </c>
     </row>
@@ -43641,7 +43641,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Росзапчасть: Сальник 55*70*8 коленвала передний без пружины [409060100503400; УАЗ] — 2 200 ₸ (сходство 100%)</t>
+          <t>УАЗ Автоград: Сальник коленвала задний 100х80х10 ОАО "УАЗ" * [0406-20-1005160; ОАО УАЗ] — 3 140 ₸ (сходство 100%)</t>
         </is>
       </c>
     </row>
@@ -44365,12 +44365,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
+          <t>Росзапчасть: Стартер 53 [511000370800000; УАЗ] — 49 500 ₸ (сходство 100%)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
           <t>Росзапчасть: Стартер 53 [523400370800000; УАЗ] — 48 400 ₸ (сходство 100%)</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Росзапчасть: Стартер 53 [511000370800000; УАЗ] — 49 500 ₸ (сходство 100%)</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -44557,12 +44557,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
+          <t>Росзапчасть: Болт ступицы колеса задний [3302-3104018; ГАЗ] — 800 ₸ (сходство 100%)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
           <t>Росзапчасть: Ремкомплект ступицы колеса [374100310300700; УАЗ] — 7 400 ₸ (сходство 100%)</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Росзапчасть: Болт ступицы колеса задний [3302-3104018; ГАЗ] — 800 ₸ (сходство 100%)</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -45895,7 +45895,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Росзапчасть: ШЕСТЕРНЯ ЗАДНЕГО ХОДА ВТОРИЧНОГО ВАЛА [315195170115500; УАЗ] — 45 100 ₸ (сходство 100%)</t>
+          <t>Росзапчасть: РОЛИК ШЕСТЕРНИ ЗАДНЕГО ХОДА 3Х23 8 А3 [4694164-807; ГАЗ] — 50 ₸ (сходство 100%)</t>
         </is>
       </c>
     </row>
@@ -46623,7 +46623,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>452-00-1702024-02</t>
+          <t>0452-00-1702024-02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -46633,7 +46633,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>УАЗ Автоград: Вилка 1-2 передачи 452 4-х синх. КПП</t>
+          <t>УАЗ Автоград: Вилка 1-2 передачи 452  с/о**</t>
         </is>
       </c>
     </row>
@@ -46812,7 +46812,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3151-3502040</t>
+          <t>3151-00--3502040-00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -46822,7 +46822,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>УАЗ Автоград: Цилиндр колесный задний д.32  ( К3205) Фенокс</t>
+          <t>УАЗ Автоград: Цилиндр колесный задний д.25 (М12) ExpertDetal **</t>
         </is>
       </c>
     </row>
@@ -48108,7 +48108,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>69-2401055</t>
+          <t>0069-00-2401055-00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -48118,7 +48118,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Росзапчасть: Шайба ступицы замочная УАЗ(уп. 10 шт)</t>
+          <t>УАЗ Автоград: Шайба замочная (ромашка) (min 10)</t>
         </is>
       </c>
     </row>
